--- a/capstone/sprint2/26-09-sprint-2-final-metrics.xlsx
+++ b/capstone/sprint2/26-09-sprint-2-final-metrics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowan\SoftwareEngineering\capstone\Stone-Ocean-Backlogs\capstone\sprint2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lewis\Software\Stone-Ocean-Backlogs\capstone\sprint2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C475811F-6EE5-48F3-A231-B8E13A084FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B78ED7E0-6F75-4FF0-9F51-F4BD5532E051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example" sheetId="8" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="46">
   <si>
     <t>Name</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>Sept 20 2026</t>
+  </si>
+  <si>
+    <t>Sept 20 2026; 9:16 PM</t>
   </si>
 </sst>
 </file>
@@ -542,7 +545,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26F2F5C-9428-EA43-9432-B11B4A37F6BD}">
   <dimension ref="A1:I1003"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -550,7 +553,7 @@
     <col min="7" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.1">
+    <row r="1" spans="1:9" ht="23.25">
       <c r="A1" s="13" t="s">
         <v>12</v>
       </c>
@@ -11675,7 +11678,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.1">
+    <row r="1" spans="1:9" ht="23.25">
       <c r="A1" s="13" t="s">
         <v>12</v>
       </c>
@@ -17998,7 +18001,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0AC37C3-57FD-E44A-8B5F-68D0EAC49E65}">
   <dimension ref="A1:I1008"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -18007,7 +18010,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.1">
+    <row r="1" spans="1:9" ht="23.25">
       <c r="A1" s="13" t="str">
         <f>Sprint4!A1</f>
         <v>Capacity, Commited, Effort, and Delivered Metric</v>
@@ -24344,7 +24347,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D22623D9-D265-E341-9D40-D4F8180816A9}">
   <dimension ref="A1:I1008"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -24353,7 +24356,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.1">
+    <row r="1" spans="1:9" ht="23.25">
       <c r="A1" s="13" t="str">
         <f>Sprint4!A1</f>
         <v>Capacity, Commited, Effort, and Delivered Metric</v>
@@ -30690,7 +30693,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE28E1FE-DF56-8B47-AF8A-1EC59E1B4672}">
   <dimension ref="A1:I1008"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -30699,7 +30702,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.1">
+    <row r="1" spans="1:9" ht="23.25">
       <c r="A1" s="13" t="str">
         <f>Sprint4!A1</f>
         <v>Capacity, Commited, Effort, and Delivered Metric</v>
@@ -37036,7 +37039,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14211EDA-4B61-5345-86E3-D319343FC73C}">
   <dimension ref="A1:I1008"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -37045,7 +37048,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.1">
+    <row r="1" spans="1:9" ht="23.25">
       <c r="A1" s="13" t="str">
         <f>Sprint4!A1</f>
         <v>Capacity, Commited, Effort, and Delivered Metric</v>
@@ -37406,9 +37409,13 @@
       <c r="A25" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="10"/>
+      <c r="B25" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="C25" s="16"/>
-      <c r="D25" s="17"/>
+      <c r="D25" s="17" t="s">
+        <v>45</v>
+      </c>
       <c r="E25" s="7"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1">

--- a/capstone/sprint2/26-09-sprint-2-final-metrics.xlsx
+++ b/capstone/sprint2/26-09-sprint-2-final-metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lewis\Software\Stone-Ocean-Backlogs\capstone\sprint2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B78ED7E0-6F75-4FF0-9F51-F4BD5532E051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070A2380-10AF-4918-A31A-8EE6391C84FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37209,7 +37209,7 @@
         <v>9</v>
       </c>
       <c r="E11" s="7">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="9">
@@ -37218,11 +37218,11 @@
       </c>
       <c r="H11" s="10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.69230769230769229</v>
       </c>
       <c r="I11" s="10">
         <f t="shared" si="1"/>
-        <v>1.0833333333333333</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1">
@@ -37306,7 +37306,7 @@
       </c>
       <c r="E16" s="7">
         <f>SUM(E9:E14)</f>
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="9">
@@ -37315,11 +37315,11 @@
       </c>
       <c r="H16" s="10">
         <f t="shared" si="2"/>
-        <v>0.88888888888888884</v>
+        <v>0.81481481481481477</v>
       </c>
       <c r="I16" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
